--- a/Result/profitability/3028.xlsx
+++ b/Result/profitability/3028.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9662500000000001</v>
+        <v>1.18625</v>
       </c>
       <c r="N2" t="n">
-        <v>7.465</v>
+        <v>7.641249999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,7 +780,7 @@
         <v>0.21</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9387500000000001</v>
+        <v>1.10125</v>
       </c>
       <c r="N3" t="n">
         <v>7.46625</v>
@@ -899,10 +899,10 @@
         <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.89</v>
+        <v>1.0275</v>
       </c>
       <c r="N4" t="n">
-        <v>7.53125</v>
+        <v>7.453749999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>0.77125</v>
+        <v>1.02875</v>
       </c>
       <c r="N5" t="n">
-        <v>7.212499999999999</v>
+        <v>7.273750000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0.79</v>
+        <v>0.9662499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>7.165</v>
+        <v>7.3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.45</v>
       </c>
       <c r="M7" t="n">
-        <v>0.74875</v>
+        <v>0.87875</v>
       </c>
       <c r="N7" t="n">
-        <v>7.231249999999999</v>
+        <v>7.215</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.52</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6699999999999999</v>
+        <v>0.5625</v>
       </c>
       <c r="N8" t="n">
-        <v>6.91875</v>
+        <v>6.725000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3028</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>19503</v>
+      </c>
+      <c r="D75" t="n">
+        <v>18031</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1472</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="G75" t="n">
+        <v>772</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.96%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-116</v>
+      </c>
+      <c r="J75" t="n">
+        <v>656</v>
+      </c>
+      <c r="K75" t="n">
+        <v>521</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.21375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7.465</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.8599999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.281967213114754</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1703296703296703</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>15.84615384615385</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.4900000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.06940509915014159</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
